--- a/data/weeks/W09.xlsx
+++ b/data/weeks/W09.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/tester/data/weeks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/weeks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9A13819-9D96-4785-A8A8-7FC85E3826C0}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_C8570FC7D454268FE34010164DC06639DFA2C1EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9384BEFE-800D-4D93-AF12-CB0799A34439}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Name</t>
   </si>
@@ -209,9 +209,6 @@
   </si>
   <si>
     <t>9881</t>
-  </si>
-  <si>
-    <t>Red*</t>
   </si>
 </sst>
 </file>
@@ -1242,8 +1239,8 @@
       <c r="B26" t="s">
         <v>57</v>
       </c>
-      <c r="C26" t="s">
-        <v>62</v>
+      <c r="C26" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D26" s="2">
         <v>5</v>
